--- a/leave_of_absence_forms/047_guest_service_training_leave_of_absence_request--leave_of_absence_forms.xlsx
+++ b/leave_of_absence_forms/047_guest_service_training_leave_of_absence_request--leave_of_absence_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'service_skills'}</t>
+          <t>service_skills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Service Skills'}</t>
+          <t>Service Skills</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product_knowledge'}</t>
+          <t>product_knowledge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product Knowledge'}</t>
+          <t>Product Knowledge</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'food_and_beverage'}</t>
+          <t>food_and_beverage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Food and Beverage'}</t>
+          <t>Food and Beverage</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'reject'}</t>
+          <t>reject</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Reject'}</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'reject'}</t>
+          <t>reject</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Reject'}</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
